--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121152685</v>
       </c>
       <c r="B5" t="n">
-        <v>91991</v>
+        <v>92001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121152685</v>
       </c>
       <c r="B5" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121152685</v>
       </c>
       <c r="B5" t="n">
-        <v>92013</v>
+        <v>92014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>121152685</v>
       </c>
       <c r="B5" t="n">
-        <v>92014</v>
+        <v>92017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 59618-2023 artfynd.xlsx
+++ b/artfynd/A 59618-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182543</v>
+        <v>112182213</v>
       </c>
       <c r="B2" t="n">
-        <v>77441</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758306</v>
+        <v>758141</v>
       </c>
       <c r="R2" t="n">
-        <v>7289343</v>
+        <v>7289289</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112182213</v>
+        <v>112182543</v>
       </c>
       <c r="B3" t="n">
-        <v>90853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758141</v>
+        <v>758306</v>
       </c>
       <c r="R3" t="n">
-        <v>7289289</v>
+        <v>7289343</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,228 +884,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>113888973</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Storsund, Nb</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>757861</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7289460</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-09-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>121152685</v>
-      </c>
-      <c r="B5" t="n">
-        <v>92017</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Storsund, Nb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>758305</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7289370</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Älvsbyn</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Älvsby</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
